--- a/dataAcquisition/Motec_MP/plottingRequest/plottingRequest_Devo.xlsx
+++ b/dataAcquisition/Motec_MP/plottingRequest/plottingRequest_Devo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SimEnv\dataAcquisition\Motec_MP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SimEnv\dataAcquisition\Motec_MP\plottingRequest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51509004-0C70-47C2-BDFF-473D312A6F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017A76E3-AFCA-46FE-9E78-6F1368AE9DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{98CBB8D2-373D-4831-8E1A-176399598E12}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{98CBB8D2-373D-4831-8E1A-176399598E12}"/>
   </bookViews>
   <sheets>
     <sheet name="plotting" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="101">
   <si>
     <t>mathFunction</t>
   </si>
@@ -267,6 +267,78 @@
   </si>
   <si>
     <t>Fastest Lap Damper</t>
+  </si>
+  <si>
+    <t>CLa_SCz_Braking_VCH</t>
+  </si>
+  <si>
+    <t>CLa_SCz_Entry_VCH</t>
+  </si>
+  <si>
+    <t>CLa_SCz_MidCrn_VCH</t>
+  </si>
+  <si>
+    <t>CLa_SCz_Exit_VCH</t>
+  </si>
+  <si>
+    <t>phase_profile</t>
+  </si>
+  <si>
+    <t>Cz Total Gated Aero Plot</t>
+  </si>
+  <si>
+    <t>Cx Binned Cx Gates</t>
+  </si>
+  <si>
+    <t>Low_Speed_Cx</t>
+  </si>
+  <si>
+    <t>Mid_Speed_Cx</t>
+  </si>
+  <si>
+    <t>High_Speed_SCx</t>
+  </si>
+  <si>
+    <t>Parity _Speed_Cx</t>
+  </si>
+  <si>
+    <t>Balance % Front</t>
+  </si>
+  <si>
+    <t>AB_Braking</t>
+  </si>
+  <si>
+    <t>AB_Entry</t>
+  </si>
+  <si>
+    <t>AB_Midcrn</t>
+  </si>
+  <si>
+    <t>AB_Exit</t>
+  </si>
+  <si>
+    <t>EFF_Braking</t>
+  </si>
+  <si>
+    <t>EFF_Entry</t>
+  </si>
+  <si>
+    <t>EFF_MidCrn</t>
+  </si>
+  <si>
+    <t>EFF_Exit</t>
+  </si>
+  <si>
+    <t>SideForce_Entry</t>
+  </si>
+  <si>
+    <t>SideForce_Midcrn</t>
+  </si>
+  <si>
+    <t>Aero Efficiency</t>
+  </si>
+  <si>
+    <t>Side Force</t>
   </si>
 </sst>
 </file>
@@ -290,7 +362,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,6 +387,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -328,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -346,6 +442,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,11 +796,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8B1EEC-F5CB-4522-AB96-C6BC3CAD72FB}">
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.21875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.109375" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.21875" bestFit="1" customWidth="1"/>
@@ -2101,7 +2217,7 @@
         <v>53</v>
       </c>
       <c r="N27" s="4">
-        <f t="shared" ref="N27:N30" si="2">IF(TRIM(P26)=TRIM(O26), N26+1, N26)</f>
+        <f t="shared" ref="N27:N35" si="2">IF(TRIM(P26)=TRIM(O26), N26+1, N26)</f>
         <v>23</v>
       </c>
       <c r="O27" s="4" t="s">
@@ -2276,7 +2392,273 @@
         <v>74</v>
       </c>
     </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="O32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L33" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="O33" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="16"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="L34" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="O34" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L35" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="O35" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P35" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>